--- a/docs/Työajan seuranta Valtteri.xlsx
+++ b/docs/Työajan seuranta Valtteri.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12C5832C-4658-4110-8DFA-84F01CBC31FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{090EBF8A-BB39-43C9-9B04-B72367ECF3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -48,13 +48,46 @@
   </si>
   <si>
     <t>Aika</t>
+  </si>
+  <si>
+    <t>low fidelity wireframe</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>Ui search (home navbar)</t>
+  </si>
+  <si>
+    <t>8h</t>
+  </si>
+  <si>
+    <t>Ui Search (home navbar search)</t>
+  </si>
+  <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>Ui search page ja now in theaters page loppuun</t>
+  </si>
+  <si>
+    <t>6.5h</t>
+  </si>
+  <si>
+    <t>Implement Login API and Auth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shared login url </t>
+  </si>
+  <si>
+    <t>5h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,15 +116,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normaali" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -107,9 +143,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 -teema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -147,7 +183,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -253,7 +289,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,7 +431,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -403,15 +439,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BC3D70-9A8B-4A59-8343-1D3356DFB267}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,7 +455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -430,11 +466,71 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -442,6 +538,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BAF6AFB37B6774A9122C6036818BC92" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c611cd0fe7e35dfe638a44e659100205">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44038759-07ae-40d4-bc3d-7c9fb0b3775b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="36a43d4c38ea7f7b42b5de64d2c1c906" ns3:_="">
     <xsd:import namespace="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
@@ -621,57 +734,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
